--- a/공정별_유해위험물질_MSDS_QR목록.xlsx
+++ b/공정별_유해위험물질_MSDS_QR목록.xlsx
@@ -696,6 +696,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -998,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1345,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>무수염산</t>
+          <t>몰튼솔트</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1337,7 +1362,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>아황산나트륨</t>
+          <t>무수염산</t>
         </is>
       </c>
       <c r="C21" s="9" t="n"/>
@@ -1354,7 +1379,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>차아염소산나트륨</t>
+          <t>아황산나트륨</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -1371,7 +1396,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>황산</t>
+          <t>차아염소산나트륨</t>
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
@@ -1381,6 +1406,23 @@
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>황산</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>클릭하여 파일 열기</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1407,8 +1449,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
 </worksheet>
 </file>